--- a/data/trans_orig/IP1006-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1006-Habitat-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149108</t>
+          <t>149060</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>287813</t>
+          <t>288206</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>189973</t>
+          <t>190597</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>208036</t>
+          <t>208315</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>402059</t>
+          <t>401281</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>406667</t>
+          <t>406663</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135166</t>
+          <t>134766</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>284845</t>
+          <t>284835</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>205861</t>
+          <t>205868</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>203143</t>
+          <t>203825</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>412316</t>
+          <t>412611</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>642</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>675075</t>
+          <t>675346</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>680360</t>
+          <t>680379</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>716410</t>
+          <t>717154</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>722016</t>
+          <t>722015</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1394046</t>
+          <t>1394312</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1401790</t>
+          <t>1401662</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7369</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>692</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8407</t>
+          <t>7771</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132441</t>
+          <t>133013</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>145729</t>
+          <t>146295</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>152417</t>
+          <t>152423</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>281082</t>
+          <t>281718</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>288803</t>
+          <t>288797</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>201594</t>
+          <t>201971</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>217971</t>
+          <t>217965</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>422007</t>
+          <t>421993</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>426725</t>
+          <t>426726</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>162584</t>
+          <t>163043</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>317689</t>
+          <t>317808</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5540</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5361</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>201542</t>
+          <t>201890</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>412021</t>
+          <t>412305</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11337</t>
+          <t>11705</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13378</t>
+          <t>13035</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>702839</t>
+          <t>702219</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>736805</t>
+          <t>736437</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>745464</t>
+          <t>745402</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1441692</t>
+          <t>1442035</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1451294</t>
+          <t>1451500</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>129774</t>
+          <t>130865</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>144626</t>
+          <t>143890</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>277167</t>
+          <t>277164</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>539</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>870</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>6668</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>200826</t>
+          <t>200610</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>206711</t>
+          <t>206708</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>220566</t>
+          <t>220735</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>425508</t>
+          <t>424938</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>430943</t>
+          <t>430736</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>163863</t>
+          <t>162612</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>318830</t>
+          <t>319468</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>658</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9470</t>
+          <t>9605</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>698133</t>
+          <t>697614</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>703767</t>
+          <t>703713</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>739583</t>
+          <t>739353</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>744220</t>
+          <t>744218</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1439745</t>
+          <t>1439610</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1447277</t>
+          <t>1447214</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1006-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1006-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3609</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>720</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4017</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4313</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3597</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>152357</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>149468</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,64%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>152357</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>149060</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,38%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>428</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>288206</t>
+          <t>287490</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3432</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1303</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4566</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4017</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,67%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3827</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>211457</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>208710</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>310</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>193860</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>190597</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>191146</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,33%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,94%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>211457</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>208315</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,2%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>631</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>401281</t>
+          <t>401021</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>406663</t>
+          <t>406665</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3051</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2638</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>2630</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2639</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>137293</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>134766</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>135179</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,62%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,79%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,09%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>460</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>284835</t>
+          <t>284844</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1756,102 +1756,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2797</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>683</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3447</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3436</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1378</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3999</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4444</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1378</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4528</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -1864,102 +1864,102 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>207129</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>205027</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,67%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>273</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>208632</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>205868</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>205879</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,67%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,35%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,36%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>207129</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>203825</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>415761</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>412695</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>417139</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>99,67%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,08%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>415761</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>412611</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>417139</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,67%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5639</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2510</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5675</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6411</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2100</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5546</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9604</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>720600</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>717061</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>722016</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1014</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>678511</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>675346</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>680379</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>674610</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>680356</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,63%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>720600</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>717154</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>722015</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1394312</t>
+          <t>1394117</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1401662</t>
+          <t>1401706</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2522</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6886</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3378</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3373</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2522</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6803</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7771</t>
+          <t>8173</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -2782,74 +2782,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>150576</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>146212</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>152419</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,5%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>135730</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>133013</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>133018</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,52%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>97,52%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,53%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>150576</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>146295</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>152423</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,35%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,56%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>390</t>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>281718</t>
+          <t>281316</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>288797</t>
+          <t>288348</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4634</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>685</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3427</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3398</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4012</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>651</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5383</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>220654</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>217343</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>316</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>204713</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>201971</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>202000</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,67%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,33%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>220654</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>217965</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,19%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>635</t>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>421993</t>
+          <t>421955</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>426726</t>
+          <t>426725</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,107 +3355,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2460</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>584</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2942</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>2929</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3016</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -3468,74 +3468,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>165401</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>163525</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>165401</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>163043</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>98,23%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>495</t>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>317808</t>
+          <t>317895</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,107 +3698,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1461</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5063</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1461</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5192</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5164</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1461</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>5077</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>205621</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>202019</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>205621</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>201890</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,49%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>554</t>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>412305</t>
+          <t>412218</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,74 +4041,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5889</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2501</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11602</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1346</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4709</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4746</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>0,67%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>5889</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2740</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>11705</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13035</t>
+          <t>12979</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -4154,74 +4154,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>742253</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>736540</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>745641</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,67%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>705582</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>702219</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>702182</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>99,33%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>742253</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>736437</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>745402</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,44%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2074</t>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1442035</t>
+          <t>1442091</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1451500</t>
+          <t>1451219</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4621,102 +4621,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>600</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2842</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3117</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4186</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4329</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1340</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4619</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -4729,74 +4729,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>147336</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>144654</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,69%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>133107</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>130865</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>130590</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,55%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>97,87%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,67%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>147336</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>143890</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,5%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,17%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>380</t>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>277164</t>
+          <t>277454</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3417</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2073</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6637</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>537</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5932</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3624</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>666</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>7257</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -5077,69 +5077,69 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>223733</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>220942</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>205174</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>200610</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>206708</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>201315</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>206710</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,14%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,74%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>223733</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>220735</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,38%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>662</t>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>424938</t>
+          <t>424349</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>430736</t>
+          <t>430940</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,107 +5302,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3198</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>634</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4061</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3775</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3202</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -5415,74 +5415,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>166039</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>163475</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>98,08%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>166039</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>162612</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,56%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>506</t>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>319468</t>
+          <t>318895</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5758,47 +5758,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6071</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2673</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>658</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6757</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6913</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5491</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9605</t>
+          <t>9152</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -6101,74 +6101,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>742845</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>738773</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>744217</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1057</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>701698</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>697614</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>703713</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>697458</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>703769</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,62%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>742845</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>739353</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>744218</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2119</t>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1439610</t>
+          <t>1440063</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1447214</t>
+          <t>1447335</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
